--- a/excel/10000(n)/RAW_Dataset.xlsx
+++ b/excel/10000(n)/RAW_Dataset.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Java-Practice\##SS2\Lab3 Sorting\excel\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -58,12 +58,316 @@
   </si>
   <si>
     <t>Trial 9</t>
+  </si>
+  <si>
+    <t>Bubble Sort</t>
+  </si>
+  <si>
+    <t>Bubble Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Insertion Sort</t>
+  </si>
+  <si>
+    <t>Insertion Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Selection Sort</t>
+  </si>
+  <si>
+    <t>Selection Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Merge Sort</t>
+  </si>
+  <si>
+    <t>Merge Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Quick Sort</t>
+  </si>
+  <si>
+    <t>Quick Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Trial 10</t>
+  </si>
+  <si>
+    <t>Trial 11</t>
+  </si>
+  <si>
+    <t>Trial 12</t>
+  </si>
+  <si>
+    <t>Trial 13</t>
+  </si>
+  <si>
+    <t>Trial 14</t>
+  </si>
+  <si>
+    <t>Trial 15</t>
+  </si>
+  <si>
+    <t>Trial 16</t>
+  </si>
+  <si>
+    <t>Trial 17</t>
+  </si>
+  <si>
+    <t>Trial 18</t>
+  </si>
+  <si>
+    <t>Trial 19</t>
+  </si>
+  <si>
+    <t>Trial 20</t>
+  </si>
+  <si>
+    <t>Trial 21</t>
+  </si>
+  <si>
+    <t>Trial 22</t>
+  </si>
+  <si>
+    <t>Trial 23</t>
+  </si>
+  <si>
+    <t>Trial 24</t>
+  </si>
+  <si>
+    <t>Trial 25</t>
+  </si>
+  <si>
+    <t>Trial 26</t>
+  </si>
+  <si>
+    <t>Trial 27</t>
+  </si>
+  <si>
+    <t>Trial 28</t>
+  </si>
+  <si>
+    <t>Trial 29</t>
+  </si>
+  <si>
+    <t>Trial 30</t>
+  </si>
+  <si>
+    <t>Trial 31</t>
+  </si>
+  <si>
+    <t>Trial 32</t>
+  </si>
+  <si>
+    <t>Trial 33</t>
+  </si>
+  <si>
+    <t>Trial 34</t>
+  </si>
+  <si>
+    <t>Trial 35</t>
+  </si>
+  <si>
+    <t>Trial 36</t>
+  </si>
+  <si>
+    <t>Trial 37</t>
+  </si>
+  <si>
+    <t>Trial 38</t>
+  </si>
+  <si>
+    <t>Trial 39</t>
+  </si>
+  <si>
+    <t>Trial 40</t>
+  </si>
+  <si>
+    <t>Trial 41</t>
+  </si>
+  <si>
+    <t>Trial 42</t>
+  </si>
+  <si>
+    <t>Trial 43</t>
+  </si>
+  <si>
+    <t>Trial 44</t>
+  </si>
+  <si>
+    <t>Trial 45</t>
+  </si>
+  <si>
+    <t>Trial 46</t>
+  </si>
+  <si>
+    <t>Trial 47</t>
+  </si>
+  <si>
+    <t>Trial 48</t>
+  </si>
+  <si>
+    <t>Trial 49</t>
+  </si>
+  <si>
+    <t>Trial 50</t>
+  </si>
+  <si>
+    <t>Trial 51</t>
+  </si>
+  <si>
+    <t>Trial 52</t>
+  </si>
+  <si>
+    <t>Trial 53</t>
+  </si>
+  <si>
+    <t>Trial 54</t>
+  </si>
+  <si>
+    <t>Trial 55</t>
+  </si>
+  <si>
+    <t>Trial 56</t>
+  </si>
+  <si>
+    <t>Trial 57</t>
+  </si>
+  <si>
+    <t>Trial 58</t>
+  </si>
+  <si>
+    <t>Trial 59</t>
+  </si>
+  <si>
+    <t>Trial 60</t>
+  </si>
+  <si>
+    <t>Trial 61</t>
+  </si>
+  <si>
+    <t>Trial 62</t>
+  </si>
+  <si>
+    <t>Trial 63</t>
+  </si>
+  <si>
+    <t>Trial 64</t>
+  </si>
+  <si>
+    <t>Trial 65</t>
+  </si>
+  <si>
+    <t>Trial 66</t>
+  </si>
+  <si>
+    <t>Trial 67</t>
+  </si>
+  <si>
+    <t>Trial 68</t>
+  </si>
+  <si>
+    <t>Trial 69</t>
+  </si>
+  <si>
+    <t>Trial 70</t>
+  </si>
+  <si>
+    <t>Trial 71</t>
+  </si>
+  <si>
+    <t>Trial 72</t>
+  </si>
+  <si>
+    <t>Trial 73</t>
+  </si>
+  <si>
+    <t>Trial 74</t>
+  </si>
+  <si>
+    <t>Trial 75</t>
+  </si>
+  <si>
+    <t>Trial 76</t>
+  </si>
+  <si>
+    <t>Trial 77</t>
+  </si>
+  <si>
+    <t>Trial 78</t>
+  </si>
+  <si>
+    <t>Trial 79</t>
+  </si>
+  <si>
+    <t>Trial 80</t>
+  </si>
+  <si>
+    <t>Trial 81</t>
+  </si>
+  <si>
+    <t>Trial 82</t>
+  </si>
+  <si>
+    <t>Trial 83</t>
+  </si>
+  <si>
+    <t>Trial 84</t>
+  </si>
+  <si>
+    <t>Trial 85</t>
+  </si>
+  <si>
+    <t>Trial 86</t>
+  </si>
+  <si>
+    <t>Trial 87</t>
+  </si>
+  <si>
+    <t>Trial 88</t>
+  </si>
+  <si>
+    <t>Trial 89</t>
+  </si>
+  <si>
+    <t>Trial 90</t>
+  </si>
+  <si>
+    <t>Trial 91</t>
+  </si>
+  <si>
+    <t>Trial 92</t>
+  </si>
+  <si>
+    <t>Trial 93</t>
+  </si>
+  <si>
+    <t>Trial 94</t>
+  </si>
+  <si>
+    <t>Trial 95</t>
+  </si>
+  <si>
+    <t>Trial 96</t>
+  </si>
+  <si>
+    <t>Trial 97</t>
+  </si>
+  <si>
+    <t>Trial 98</t>
+  </si>
+  <si>
+    <t>Trial 99</t>
+  </si>
+  <si>
+    <t>Trial 100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -388,11 +692,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:CX11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.77734375"/>
+    <col min="2" max="2" customWidth="true" width="13.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.5">
@@ -402,32 +706,3385 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>10</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="Y1" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="Z1" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="AA1" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="AB1" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="AC1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="AD1" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="AE1" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="AF1" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="AG1" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="AH1" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="AI1" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="AJ1" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="AK1" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="AL1" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="AM1" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="AN1" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="AO1" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="AP1" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="AQ1" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="AR1" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="AS1" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="AT1" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="AU1" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="AV1" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="AW1" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="AX1" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="AY1" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="AZ1" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BA1" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="BB1" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="BC1" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="BD1" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="BE1" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="BF1" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="BG1" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="BH1" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="BI1" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="BJ1" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="BK1" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="BL1" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="BM1" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="BN1" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="BO1" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="BP1" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="BQ1" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="BR1" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="BS1" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BT1" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="BU1" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="BV1" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="BW1" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="BX1" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="BY1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="BZ1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="CA1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="CB1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="CC1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="CD1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="CE1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="CF1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="CG1" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="CH1" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="CI1" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="CJ1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="CK1" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="CL1" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="CM1" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="CN1" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="CO1" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="CP1" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="CQ1" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="CR1" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="CS1" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="CT1" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="CU1" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="CV1" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="CW1" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="CX1" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.9663E7</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>6.69314E7</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>8.64861E7</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>6.48306E7</v>
+      </c>
+      <c r="G2" t="n" s="0">
+        <v>6.79665E7</v>
+      </c>
+      <c r="H2" t="n" s="0">
+        <v>6.67024E7</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>6.61487E7</v>
+      </c>
+      <c r="J2" t="n" s="0">
+        <v>6.61395E7</v>
+      </c>
+      <c r="K2" t="n" s="0">
+        <v>6.6656E7</v>
+      </c>
+      <c r="L2" t="n" s="0">
+        <v>8.53567E7</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>8.44957E7</v>
+      </c>
+      <c r="N2" t="n" s="0">
+        <v>8.43521E7</v>
+      </c>
+      <c r="O2" t="n" s="0">
+        <v>8.56247E7</v>
+      </c>
+      <c r="P2" t="n" s="0">
+        <v>8.50712E7</v>
+      </c>
+      <c r="Q2" t="n" s="0">
+        <v>1.056247E8</v>
+      </c>
+      <c r="R2" t="n" s="0">
+        <v>8.45055E7</v>
+      </c>
+      <c r="S2" t="n" s="0">
+        <v>8.59658E7</v>
+      </c>
+      <c r="T2" t="n" s="0">
+        <v>8.30583E7</v>
+      </c>
+      <c r="U2" t="n" s="0">
+        <v>8.54699E7</v>
+      </c>
+      <c r="V2" t="n" s="0">
+        <v>8.39447E7</v>
+      </c>
+      <c r="W2" t="n" s="0">
+        <v>8.40683E7</v>
+      </c>
+      <c r="X2" t="n" s="0">
+        <v>8.91165E7</v>
+      </c>
+      <c r="Y2" t="n" s="0">
+        <v>8.38239E7</v>
+      </c>
+      <c r="Z2" t="n" s="0">
+        <v>8.4349E7</v>
+      </c>
+      <c r="AA2" t="n" s="0">
+        <v>8.49134E7</v>
+      </c>
+      <c r="AB2" t="n" s="0">
+        <v>8.48787E7</v>
+      </c>
+      <c r="AC2" t="n" s="0">
+        <v>8.60665E7</v>
+      </c>
+      <c r="AD2" t="n" s="0">
+        <v>8.5004E7</v>
+      </c>
+      <c r="AE2" t="n" s="0">
+        <v>8.33958E7</v>
+      </c>
+      <c r="AF2" t="n" s="0">
+        <v>8.40381E7</v>
+      </c>
+      <c r="AG2" t="n" s="0">
+        <v>8.37662E7</v>
+      </c>
+      <c r="AH2" t="n" s="0">
+        <v>8.51802E7</v>
+      </c>
+      <c r="AI2" t="n" s="0">
+        <v>8.45953E7</v>
+      </c>
+      <c r="AJ2" t="n" s="0">
+        <v>8.68824E7</v>
+      </c>
+      <c r="AK2" t="n" s="0">
+        <v>8.9481E7</v>
+      </c>
+      <c r="AL2" t="n" s="0">
+        <v>8.56435E7</v>
+      </c>
+      <c r="AM2" t="n" s="0">
+        <v>8.75673E7</v>
+      </c>
+      <c r="AN2" t="n" s="0">
+        <v>8.41917E7</v>
+      </c>
+      <c r="AO2" t="n" s="0">
+        <v>8.23264E7</v>
+      </c>
+      <c r="AP2" t="n" s="0">
+        <v>8.58974E7</v>
+      </c>
+      <c r="AQ2" t="n" s="0">
+        <v>8.96913E7</v>
+      </c>
+      <c r="AR2" t="n" s="0">
+        <v>9.46299E7</v>
+      </c>
+      <c r="AS2" t="n" s="0">
+        <v>8.5774E7</v>
+      </c>
+      <c r="AT2" t="n" s="0">
+        <v>8.52043E7</v>
+      </c>
+      <c r="AU2" t="n" s="0">
+        <v>8.47683E7</v>
+      </c>
+      <c r="AV2" t="n" s="0">
+        <v>8.54044E7</v>
+      </c>
+      <c r="AW2" t="n" s="0">
+        <v>8.44234E7</v>
+      </c>
+      <c r="AX2" t="n" s="0">
+        <v>8.51175E7</v>
+      </c>
+      <c r="AY2" t="n" s="0">
+        <v>8.45844E7</v>
+      </c>
+      <c r="AZ2" t="n" s="0">
+        <v>8.50879E7</v>
+      </c>
+      <c r="BA2" t="n" s="0">
+        <v>8.73139E7</v>
+      </c>
+      <c r="BB2" t="n" s="0">
+        <v>8.55454E7</v>
+      </c>
+      <c r="BC2" t="n" s="0">
+        <v>9.01439E7</v>
+      </c>
+      <c r="BD2" t="n" s="0">
+        <v>8.43718E7</v>
+      </c>
+      <c r="BE2" t="n" s="0">
+        <v>8.39981E7</v>
+      </c>
+      <c r="BF2" t="n" s="0">
+        <v>8.62342E7</v>
+      </c>
+      <c r="BG2" t="n" s="0">
+        <v>1.060844E8</v>
+      </c>
+      <c r="BH2" t="n" s="0">
+        <v>1.003982E8</v>
+      </c>
+      <c r="BI2" t="n" s="0">
+        <v>8.52249E7</v>
+      </c>
+      <c r="BJ2" t="n" s="0">
+        <v>8.69263E7</v>
+      </c>
+      <c r="BK2" t="n" s="0">
+        <v>8.40195E7</v>
+      </c>
+      <c r="BL2" t="n" s="0">
+        <v>8.92011E7</v>
+      </c>
+      <c r="BM2" t="n" s="0">
+        <v>8.49791E7</v>
+      </c>
+      <c r="BN2" t="n" s="0">
+        <v>8.48585E7</v>
+      </c>
+      <c r="BO2" t="n" s="0">
+        <v>9.21407E7</v>
+      </c>
+      <c r="BP2" t="n" s="0">
+        <v>8.90873E7</v>
+      </c>
+      <c r="BQ2" t="n" s="0">
+        <v>8.98362E7</v>
+      </c>
+      <c r="BR2" t="n" s="0">
+        <v>8.98535E7</v>
+      </c>
+      <c r="BS2" t="n" s="0">
+        <v>9.02559E7</v>
+      </c>
+      <c r="BT2" t="n" s="0">
+        <v>9.01453E7</v>
+      </c>
+      <c r="BU2" t="n" s="0">
+        <v>9.0349E7</v>
+      </c>
+      <c r="BV2" t="n" s="0">
+        <v>1.050659E8</v>
+      </c>
+      <c r="BW2" t="n" s="0">
+        <v>9.14121E7</v>
+      </c>
+      <c r="BX2" t="n" s="0">
+        <v>8.24105E7</v>
+      </c>
+      <c r="BY2" t="n" s="0">
+        <v>8.52025E7</v>
+      </c>
+      <c r="BZ2" t="n" s="0">
+        <v>8.69511E7</v>
+      </c>
+      <c r="CA2" t="n" s="0">
+        <v>8.86787E7</v>
+      </c>
+      <c r="CB2" t="n" s="0">
+        <v>1.000176E8</v>
+      </c>
+      <c r="CC2" t="n" s="0">
+        <v>9.5029E7</v>
+      </c>
+      <c r="CD2" t="n" s="0">
+        <v>9.56076E7</v>
+      </c>
+      <c r="CE2" t="n" s="0">
+        <v>8.44415E7</v>
+      </c>
+      <c r="CF2" t="n" s="0">
+        <v>8.40916E7</v>
+      </c>
+      <c r="CG2" t="n" s="0">
+        <v>8.83297E7</v>
+      </c>
+      <c r="CH2" t="n" s="0">
+        <v>8.44117E7</v>
+      </c>
+      <c r="CI2" t="n" s="0">
+        <v>8.4746E7</v>
+      </c>
+      <c r="CJ2" t="n" s="0">
+        <v>8.5589E7</v>
+      </c>
+      <c r="CK2" t="n" s="0">
+        <v>8.57057E7</v>
+      </c>
+      <c r="CL2" t="n" s="0">
+        <v>8.55633E7</v>
+      </c>
+      <c r="CM2" t="n" s="0">
+        <v>8.46414E7</v>
+      </c>
+      <c r="CN2" t="n" s="0">
+        <v>9.19386E7</v>
+      </c>
+      <c r="CO2" t="n" s="0">
+        <v>8.49484E7</v>
+      </c>
+      <c r="CP2" t="n" s="0">
+        <v>8.41512E7</v>
+      </c>
+      <c r="CQ2" t="n" s="0">
+        <v>8.54378E7</v>
+      </c>
+      <c r="CR2" t="n" s="0">
+        <v>8.8661E7</v>
+      </c>
+      <c r="CS2" t="n" s="0">
+        <v>8.62369E7</v>
+      </c>
+      <c r="CT2" t="n" s="0">
+        <v>8.64671E7</v>
+      </c>
+      <c r="CU2" t="n" s="0">
+        <v>8.81065E7</v>
+      </c>
+      <c r="CV2" t="n" s="0">
+        <v>8.4622E7</v>
+      </c>
+      <c r="CW2" t="n" s="0">
+        <v>1.017787E8</v>
+      </c>
+      <c r="CX2" t="n" s="0">
+        <v>8.50808E7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>6.88036E7</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>6.5894E7</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>9.04496E7</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>6.37616E7</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>6.67804E7</v>
+      </c>
+      <c r="H3" t="n" s="0">
+        <v>6.6539E7</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>6.55726E7</v>
+      </c>
+      <c r="J3" t="n" s="0">
+        <v>6.60459E7</v>
+      </c>
+      <c r="K3" t="n" s="0">
+        <v>6.56164E7</v>
+      </c>
+      <c r="L3" t="n" s="0">
+        <v>9.12773E7</v>
+      </c>
+      <c r="M3" t="n" s="0">
+        <v>8.35014E7</v>
+      </c>
+      <c r="N3" t="n" s="0">
+        <v>8.45767E7</v>
+      </c>
+      <c r="O3" t="n" s="0">
+        <v>8.73362E7</v>
+      </c>
+      <c r="P3" t="n" s="0">
+        <v>8.49683E7</v>
+      </c>
+      <c r="Q3" t="n" s="0">
+        <v>8.8843E7</v>
+      </c>
+      <c r="R3" t="n" s="0">
+        <v>9.08176E7</v>
+      </c>
+      <c r="S3" t="n" s="0">
+        <v>8.44243E7</v>
+      </c>
+      <c r="T3" t="n" s="0">
+        <v>8.37885E7</v>
+      </c>
+      <c r="U3" t="n" s="0">
+        <v>8.42335E7</v>
+      </c>
+      <c r="V3" t="n" s="0">
+        <v>8.39708E7</v>
+      </c>
+      <c r="W3" t="n" s="0">
+        <v>8.3133E7</v>
+      </c>
+      <c r="X3" t="n" s="0">
+        <v>8.638E7</v>
+      </c>
+      <c r="Y3" t="n" s="0">
+        <v>8.29937E7</v>
+      </c>
+      <c r="Z3" t="n" s="0">
+        <v>8.43453E7</v>
+      </c>
+      <c r="AA3" t="n" s="0">
+        <v>8.74087E7</v>
+      </c>
+      <c r="AB3" t="n" s="0">
+        <v>8.4093E7</v>
+      </c>
+      <c r="AC3" t="n" s="0">
+        <v>8.32993E7</v>
+      </c>
+      <c r="AD3" t="n" s="0">
+        <v>8.38027E7</v>
+      </c>
+      <c r="AE3" t="n" s="0">
+        <v>8.46546E7</v>
+      </c>
+      <c r="AF3" t="n" s="0">
+        <v>8.50968E7</v>
+      </c>
+      <c r="AG3" t="n" s="0">
+        <v>8.62846E7</v>
+      </c>
+      <c r="AH3" t="n" s="0">
+        <v>8.94506E7</v>
+      </c>
+      <c r="AI3" t="n" s="0">
+        <v>8.39513E7</v>
+      </c>
+      <c r="AJ3" t="n" s="0">
+        <v>8.69646E7</v>
+      </c>
+      <c r="AK3" t="n" s="0">
+        <v>8.80723E7</v>
+      </c>
+      <c r="AL3" t="n" s="0">
+        <v>8.60182E7</v>
+      </c>
+      <c r="AM3" t="n" s="0">
+        <v>8.36595E7</v>
+      </c>
+      <c r="AN3" t="n" s="0">
+        <v>8.54433E7</v>
+      </c>
+      <c r="AO3" t="n" s="0">
+        <v>8.42062E7</v>
+      </c>
+      <c r="AP3" t="n" s="0">
+        <v>8.83075E7</v>
+      </c>
+      <c r="AQ3" t="n" s="0">
+        <v>9.66304E7</v>
+      </c>
+      <c r="AR3" t="n" s="0">
+        <v>8.67155E7</v>
+      </c>
+      <c r="AS3" t="n" s="0">
+        <v>8.39357E7</v>
+      </c>
+      <c r="AT3" t="n" s="0">
+        <v>8.71926E7</v>
+      </c>
+      <c r="AU3" t="n" s="0">
+        <v>8.38944E7</v>
+      </c>
+      <c r="AV3" t="n" s="0">
+        <v>8.32976E7</v>
+      </c>
+      <c r="AW3" t="n" s="0">
+        <v>8.78188E7</v>
+      </c>
+      <c r="AX3" t="n" s="0">
+        <v>8.5515E7</v>
+      </c>
+      <c r="AY3" t="n" s="0">
+        <v>8.74037E7</v>
+      </c>
+      <c r="AZ3" t="n" s="0">
+        <v>8.52822E7</v>
+      </c>
+      <c r="BA3" t="n" s="0">
+        <v>8.43669E7</v>
+      </c>
+      <c r="BB3" t="n" s="0">
+        <v>8.46649E7</v>
+      </c>
+      <c r="BC3" t="n" s="0">
+        <v>8.50276E7</v>
+      </c>
+      <c r="BD3" t="n" s="0">
+        <v>8.45397E7</v>
+      </c>
+      <c r="BE3" t="n" s="0">
+        <v>8.31751E7</v>
+      </c>
+      <c r="BF3" t="n" s="0">
+        <v>8.70419E7</v>
+      </c>
+      <c r="BG3" t="n" s="0">
+        <v>9.30489E7</v>
+      </c>
+      <c r="BH3" t="n" s="0">
+        <v>9.13486E7</v>
+      </c>
+      <c r="BI3" t="n" s="0">
+        <v>8.60213E7</v>
+      </c>
+      <c r="BJ3" t="n" s="0">
+        <v>8.7216E7</v>
+      </c>
+      <c r="BK3" t="n" s="0">
+        <v>8.73433E7</v>
+      </c>
+      <c r="BL3" t="n" s="0">
+        <v>8.43814E7</v>
+      </c>
+      <c r="BM3" t="n" s="0">
+        <v>8.3402E7</v>
+      </c>
+      <c r="BN3" t="n" s="0">
+        <v>8.38973E7</v>
+      </c>
+      <c r="BO3" t="n" s="0">
+        <v>8.83482E7</v>
+      </c>
+      <c r="BP3" t="n" s="0">
+        <v>9.0066E7</v>
+      </c>
+      <c r="BQ3" t="n" s="0">
+        <v>8.98841E7</v>
+      </c>
+      <c r="BR3" t="n" s="0">
+        <v>8.95911E7</v>
+      </c>
+      <c r="BS3" t="n" s="0">
+        <v>8.69012E7</v>
+      </c>
+      <c r="BT3" t="n" s="0">
+        <v>8.92016E7</v>
+      </c>
+      <c r="BU3" t="n" s="0">
+        <v>9.07003E7</v>
+      </c>
+      <c r="BV3" t="n" s="0">
+        <v>8.97581E7</v>
+      </c>
+      <c r="BW3" t="n" s="0">
+        <v>9.04745E7</v>
+      </c>
+      <c r="BX3" t="n" s="0">
+        <v>8.32847E7</v>
+      </c>
+      <c r="BY3" t="n" s="0">
+        <v>8.76116E7</v>
+      </c>
+      <c r="BZ3" t="n" s="0">
+        <v>8.61929E7</v>
+      </c>
+      <c r="CA3" t="n" s="0">
+        <v>8.74105E7</v>
+      </c>
+      <c r="CB3" t="n" s="0">
+        <v>1.013032E8</v>
+      </c>
+      <c r="CC3" t="n" s="0">
+        <v>1.02408E8</v>
+      </c>
+      <c r="CD3" t="n" s="0">
+        <v>8.51355E7</v>
+      </c>
+      <c r="CE3" t="n" s="0">
+        <v>8.57608E7</v>
+      </c>
+      <c r="CF3" t="n" s="0">
+        <v>8.70363E7</v>
+      </c>
+      <c r="CG3" t="n" s="0">
+        <v>8.84281E7</v>
+      </c>
+      <c r="CH3" t="n" s="0">
+        <v>8.49137E7</v>
+      </c>
+      <c r="CI3" t="n" s="0">
+        <v>8.43998E7</v>
+      </c>
+      <c r="CJ3" t="n" s="0">
+        <v>8.30586E7</v>
+      </c>
+      <c r="CK3" t="n" s="0">
+        <v>8.65004E7</v>
+      </c>
+      <c r="CL3" t="n" s="0">
+        <v>8.43343E7</v>
+      </c>
+      <c r="CM3" t="n" s="0">
+        <v>8.403E7</v>
+      </c>
+      <c r="CN3" t="n" s="0">
+        <v>9.05872E7</v>
+      </c>
+      <c r="CO3" t="n" s="0">
+        <v>8.46917E7</v>
+      </c>
+      <c r="CP3" t="n" s="0">
+        <v>8.50899E7</v>
+      </c>
+      <c r="CQ3" t="n" s="0">
+        <v>8.28517E7</v>
+      </c>
+      <c r="CR3" t="n" s="0">
+        <v>8.51692E7</v>
+      </c>
+      <c r="CS3" t="n" s="0">
+        <v>8.41458E7</v>
+      </c>
+      <c r="CT3" t="n" s="0">
+        <v>8.76136E7</v>
+      </c>
+      <c r="CU3" t="n" s="0">
+        <v>8.53058E7</v>
+      </c>
+      <c r="CV3" t="n" s="0">
+        <v>8.70166E7</v>
+      </c>
+      <c r="CW3" t="n" s="0">
+        <v>8.36743E7</v>
+      </c>
+      <c r="CX3" t="n" s="0">
+        <v>8.41086E7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>1.64863E7</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>1.40618E7</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>1.37497E7</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>3495900.0</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>3638100.0</v>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>3831800.0</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>3662800.0</v>
+      </c>
+      <c r="J4" t="n" s="0">
+        <v>3866900.0</v>
+      </c>
+      <c r="K4" t="n" s="0">
+        <v>3685500.0</v>
+      </c>
+      <c r="L4" t="n" s="0">
+        <v>3323900.0</v>
+      </c>
+      <c r="M4" t="n" s="0">
+        <v>3472000.0</v>
+      </c>
+      <c r="N4" t="n" s="0">
+        <v>3548200.0</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>3434700.0</v>
+      </c>
+      <c r="P4" t="n" s="0">
+        <v>3325900.0</v>
+      </c>
+      <c r="Q4" t="n" s="0">
+        <v>3287700.0</v>
+      </c>
+      <c r="R4" t="n" s="0">
+        <v>3325500.0</v>
+      </c>
+      <c r="S4" t="n" s="0">
+        <v>3908700.0</v>
+      </c>
+      <c r="T4" t="n" s="0">
+        <v>3335000.0</v>
+      </c>
+      <c r="U4" t="n" s="0">
+        <v>3434000.0</v>
+      </c>
+      <c r="V4" t="n" s="0">
+        <v>3642500.0</v>
+      </c>
+      <c r="W4" t="n" s="0">
+        <v>5648400.0</v>
+      </c>
+      <c r="X4" t="n" s="0">
+        <v>3322400.0</v>
+      </c>
+      <c r="Y4" t="n" s="0">
+        <v>3563800.0</v>
+      </c>
+      <c r="Z4" t="n" s="0">
+        <v>4064300.0</v>
+      </c>
+      <c r="AA4" t="n" s="0">
+        <v>3508900.0</v>
+      </c>
+      <c r="AB4" t="n" s="0">
+        <v>3811900.0</v>
+      </c>
+      <c r="AC4" t="n" s="0">
+        <v>3786100.0</v>
+      </c>
+      <c r="AD4" t="n" s="0">
+        <v>3382800.0</v>
+      </c>
+      <c r="AE4" t="n" s="0">
+        <v>3688700.0</v>
+      </c>
+      <c r="AF4" t="n" s="0">
+        <v>3596200.0</v>
+      </c>
+      <c r="AG4" t="n" s="0">
+        <v>3555500.0</v>
+      </c>
+      <c r="AH4" t="n" s="0">
+        <v>3972700.0</v>
+      </c>
+      <c r="AI4" t="n" s="0">
+        <v>3358600.0</v>
+      </c>
+      <c r="AJ4" t="n" s="0">
+        <v>3731000.0</v>
+      </c>
+      <c r="AK4" t="n" s="0">
+        <v>3564800.0</v>
+      </c>
+      <c r="AL4" t="n" s="0">
+        <v>3683500.0</v>
+      </c>
+      <c r="AM4" t="n" s="0">
+        <v>3563500.0</v>
+      </c>
+      <c r="AN4" t="n" s="0">
+        <v>3903700.0</v>
+      </c>
+      <c r="AO4" t="n" s="0">
+        <v>3716300.0</v>
+      </c>
+      <c r="AP4" t="n" s="0">
+        <v>3688500.0</v>
+      </c>
+      <c r="AQ4" t="n" s="0">
+        <v>3823000.0</v>
+      </c>
+      <c r="AR4" t="n" s="0">
+        <v>3391600.0</v>
+      </c>
+      <c r="AS4" t="n" s="0">
+        <v>3696100.0</v>
+      </c>
+      <c r="AT4" t="n" s="0">
+        <v>3702800.0</v>
+      </c>
+      <c r="AU4" t="n" s="0">
+        <v>3273200.0</v>
+      </c>
+      <c r="AV4" t="n" s="0">
+        <v>3579200.0</v>
+      </c>
+      <c r="AW4" t="n" s="0">
+        <v>3275800.0</v>
+      </c>
+      <c r="AX4" t="n" s="0">
+        <v>4023200.0</v>
+      </c>
+      <c r="AY4" t="n" s="0">
+        <v>3569000.0</v>
+      </c>
+      <c r="AZ4" t="n" s="0">
+        <v>3758300.0</v>
+      </c>
+      <c r="BA4" t="n" s="0">
+        <v>3703600.0</v>
+      </c>
+      <c r="BB4" t="n" s="0">
+        <v>3411700.0</v>
+      </c>
+      <c r="BC4" t="n" s="0">
+        <v>3763000.0</v>
+      </c>
+      <c r="BD4" t="n" s="0">
+        <v>3454100.0</v>
+      </c>
+      <c r="BE4" t="n" s="0">
+        <v>3338800.0</v>
+      </c>
+      <c r="BF4" t="n" s="0">
+        <v>3702900.0</v>
+      </c>
+      <c r="BG4" t="n" s="0">
+        <v>3527300.0</v>
+      </c>
+      <c r="BH4" t="n" s="0">
+        <v>3318400.0</v>
+      </c>
+      <c r="BI4" t="n" s="0">
+        <v>3321900.0</v>
+      </c>
+      <c r="BJ4" t="n" s="0">
+        <v>3408700.0</v>
+      </c>
+      <c r="BK4" t="n" s="0">
+        <v>3515900.0</v>
+      </c>
+      <c r="BL4" t="n" s="0">
+        <v>3538500.0</v>
+      </c>
+      <c r="BM4" t="n" s="0">
+        <v>3487000.0</v>
+      </c>
+      <c r="BN4" t="n" s="0">
+        <v>3603100.0</v>
+      </c>
+      <c r="BO4" t="n" s="0">
+        <v>3553800.0</v>
+      </c>
+      <c r="BP4" t="n" s="0">
+        <v>3601500.0</v>
+      </c>
+      <c r="BQ4" t="n" s="0">
+        <v>3771000.0</v>
+      </c>
+      <c r="BR4" t="n" s="0">
+        <v>3435500.0</v>
+      </c>
+      <c r="BS4" t="n" s="0">
+        <v>3810100.0</v>
+      </c>
+      <c r="BT4" t="n" s="0">
+        <v>3660800.0</v>
+      </c>
+      <c r="BU4" t="n" s="0">
+        <v>3682000.0</v>
+      </c>
+      <c r="BV4" t="n" s="0">
+        <v>3599400.0</v>
+      </c>
+      <c r="BW4" t="n" s="0">
+        <v>3728000.0</v>
+      </c>
+      <c r="BX4" t="n" s="0">
+        <v>3668200.0</v>
+      </c>
+      <c r="BY4" t="n" s="0">
+        <v>3386100.0</v>
+      </c>
+      <c r="BZ4" t="n" s="0">
+        <v>3789400.0</v>
+      </c>
+      <c r="CA4" t="n" s="0">
+        <v>3842300.0</v>
+      </c>
+      <c r="CB4" t="n" s="0">
+        <v>4548600.0</v>
+      </c>
+      <c r="CC4" t="n" s="0">
+        <v>3721000.0</v>
+      </c>
+      <c r="CD4" t="n" s="0">
+        <v>3550200.0</v>
+      </c>
+      <c r="CE4" t="n" s="0">
+        <v>3648500.0</v>
+      </c>
+      <c r="CF4" t="n" s="0">
+        <v>3634500.0</v>
+      </c>
+      <c r="CG4" t="n" s="0">
+        <v>3488400.0</v>
+      </c>
+      <c r="CH4" t="n" s="0">
+        <v>3578400.0</v>
+      </c>
+      <c r="CI4" t="n" s="0">
+        <v>3602900.0</v>
+      </c>
+      <c r="CJ4" t="n" s="0">
+        <v>3592200.0</v>
+      </c>
+      <c r="CK4" t="n" s="0">
+        <v>3620100.0</v>
+      </c>
+      <c r="CL4" t="n" s="0">
+        <v>3297300.0</v>
+      </c>
+      <c r="CM4" t="n" s="0">
+        <v>4816200.0</v>
+      </c>
+      <c r="CN4" t="n" s="0">
+        <v>3332900.0</v>
+      </c>
+      <c r="CO4" t="n" s="0">
+        <v>3406100.0</v>
+      </c>
+      <c r="CP4" t="n" s="0">
+        <v>3491100.0</v>
+      </c>
+      <c r="CQ4" t="n" s="0">
+        <v>3317900.0</v>
+      </c>
+      <c r="CR4" t="n" s="0">
+        <v>3388000.0</v>
+      </c>
+      <c r="CS4" t="n" s="0">
+        <v>3772500.0</v>
+      </c>
+      <c r="CT4" t="n" s="0">
+        <v>3480300.0</v>
+      </c>
+      <c r="CU4" t="n" s="0">
+        <v>3324800.0</v>
+      </c>
+      <c r="CV4" t="n" s="0">
+        <v>3563700.0</v>
+      </c>
+      <c r="CW4" t="n" s="0">
+        <v>3461700.0</v>
+      </c>
+      <c r="CX4" t="n" s="0">
+        <v>3397700.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>1.55267E7</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>1.34882E7</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>1.31732E7</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>3315100.0</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>3515900.0</v>
+      </c>
+      <c r="H5" t="n" s="0">
+        <v>3593400.0</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>3300300.0</v>
+      </c>
+      <c r="J5" t="n" s="0">
+        <v>3354200.0</v>
+      </c>
+      <c r="K5" t="n" s="0">
+        <v>3480400.0</v>
+      </c>
+      <c r="L5" t="n" s="0">
+        <v>3405700.0</v>
+      </c>
+      <c r="M5" t="n" s="0">
+        <v>3435600.0</v>
+      </c>
+      <c r="N5" t="n" s="0">
+        <v>3508600.0</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>3362300.0</v>
+      </c>
+      <c r="P5" t="n" s="0">
+        <v>3567300.0</v>
+      </c>
+      <c r="Q5" t="n" s="0">
+        <v>3363600.0</v>
+      </c>
+      <c r="R5" t="n" s="0">
+        <v>3347400.0</v>
+      </c>
+      <c r="S5" t="n" s="0">
+        <v>3577300.0</v>
+      </c>
+      <c r="T5" t="n" s="0">
+        <v>3377900.0</v>
+      </c>
+      <c r="U5" t="n" s="0">
+        <v>3645500.0</v>
+      </c>
+      <c r="V5" t="n" s="0">
+        <v>3503100.0</v>
+      </c>
+      <c r="W5" t="n" s="0">
+        <v>4038700.0</v>
+      </c>
+      <c r="X5" t="n" s="0">
+        <v>3542500.0</v>
+      </c>
+      <c r="Y5" t="n" s="0">
+        <v>3917100.0</v>
+      </c>
+      <c r="Z5" t="n" s="0">
+        <v>3537100.0</v>
+      </c>
+      <c r="AA5" t="n" s="0">
+        <v>3332000.0</v>
+      </c>
+      <c r="AB5" t="n" s="0">
+        <v>3847500.0</v>
+      </c>
+      <c r="AC5" t="n" s="0">
+        <v>3555100.0</v>
+      </c>
+      <c r="AD5" t="n" s="0">
+        <v>3512400.0</v>
+      </c>
+      <c r="AE5" t="n" s="0">
+        <v>3375600.0</v>
+      </c>
+      <c r="AF5" t="n" s="0">
+        <v>3323500.0</v>
+      </c>
+      <c r="AG5" t="n" s="0">
+        <v>3289500.0</v>
+      </c>
+      <c r="AH5" t="n" s="0">
+        <v>3330300.0</v>
+      </c>
+      <c r="AI5" t="n" s="0">
+        <v>3589000.0</v>
+      </c>
+      <c r="AJ5" t="n" s="0">
+        <v>3506100.0</v>
+      </c>
+      <c r="AK5" t="n" s="0">
+        <v>3544800.0</v>
+      </c>
+      <c r="AL5" t="n" s="0">
+        <v>3444500.0</v>
+      </c>
+      <c r="AM5" t="n" s="0">
+        <v>3335500.0</v>
+      </c>
+      <c r="AN5" t="n" s="0">
+        <v>3347200.0</v>
+      </c>
+      <c r="AO5" t="n" s="0">
+        <v>3343900.0</v>
+      </c>
+      <c r="AP5" t="n" s="0">
+        <v>3586200.0</v>
+      </c>
+      <c r="AQ5" t="n" s="0">
+        <v>3786900.0</v>
+      </c>
+      <c r="AR5" t="n" s="0">
+        <v>3322800.0</v>
+      </c>
+      <c r="AS5" t="n" s="0">
+        <v>3325600.0</v>
+      </c>
+      <c r="AT5" t="n" s="0">
+        <v>3484200.0</v>
+      </c>
+      <c r="AU5" t="n" s="0">
+        <v>3281200.0</v>
+      </c>
+      <c r="AV5" t="n" s="0">
+        <v>3708700.0</v>
+      </c>
+      <c r="AW5" t="n" s="0">
+        <v>3558700.0</v>
+      </c>
+      <c r="AX5" t="n" s="0">
+        <v>3380900.0</v>
+      </c>
+      <c r="AY5" t="n" s="0">
+        <v>3382700.0</v>
+      </c>
+      <c r="AZ5" t="n" s="0">
+        <v>3293700.0</v>
+      </c>
+      <c r="BA5" t="n" s="0">
+        <v>3519000.0</v>
+      </c>
+      <c r="BB5" t="n" s="0">
+        <v>3529800.0</v>
+      </c>
+      <c r="BC5" t="n" s="0">
+        <v>3307500.0</v>
+      </c>
+      <c r="BD5" t="n" s="0">
+        <v>3424300.0</v>
+      </c>
+      <c r="BE5" t="n" s="0">
+        <v>3807000.0</v>
+      </c>
+      <c r="BF5" t="n" s="0">
+        <v>3429300.0</v>
+      </c>
+      <c r="BG5" t="n" s="0">
+        <v>3560800.0</v>
+      </c>
+      <c r="BH5" t="n" s="0">
+        <v>3453700.0</v>
+      </c>
+      <c r="BI5" t="n" s="0">
+        <v>3549900.0</v>
+      </c>
+      <c r="BJ5" t="n" s="0">
+        <v>3361200.0</v>
+      </c>
+      <c r="BK5" t="n" s="0">
+        <v>3289300.0</v>
+      </c>
+      <c r="BL5" t="n" s="0">
+        <v>3453900.0</v>
+      </c>
+      <c r="BM5" t="n" s="0">
+        <v>3315400.0</v>
+      </c>
+      <c r="BN5" t="n" s="0">
+        <v>3657700.0</v>
+      </c>
+      <c r="BO5" t="n" s="0">
+        <v>3581700.0</v>
+      </c>
+      <c r="BP5" t="n" s="0">
+        <v>3582400.0</v>
+      </c>
+      <c r="BQ5" t="n" s="0">
+        <v>3585000.0</v>
+      </c>
+      <c r="BR5" t="n" s="0">
+        <v>3408000.0</v>
+      </c>
+      <c r="BS5" t="n" s="0">
+        <v>3620000.0</v>
+      </c>
+      <c r="BT5" t="n" s="0">
+        <v>3571500.0</v>
+      </c>
+      <c r="BU5" t="n" s="0">
+        <v>3605300.0</v>
+      </c>
+      <c r="BV5" t="n" s="0">
+        <v>3613700.0</v>
+      </c>
+      <c r="BW5" t="n" s="0">
+        <v>3944300.0</v>
+      </c>
+      <c r="BX5" t="n" s="0">
+        <v>3512600.0</v>
+      </c>
+      <c r="BY5" t="n" s="0">
+        <v>4898000.0</v>
+      </c>
+      <c r="BZ5" t="n" s="0">
+        <v>3488900.0</v>
+      </c>
+      <c r="CA5" t="n" s="0">
+        <v>3663800.0</v>
+      </c>
+      <c r="CB5" t="n" s="0">
+        <v>3787800.0</v>
+      </c>
+      <c r="CC5" t="n" s="0">
+        <v>3847200.0</v>
+      </c>
+      <c r="CD5" t="n" s="0">
+        <v>3374600.0</v>
+      </c>
+      <c r="CE5" t="n" s="0">
+        <v>3576100.0</v>
+      </c>
+      <c r="CF5" t="n" s="0">
+        <v>3440400.0</v>
+      </c>
+      <c r="CG5" t="n" s="0">
+        <v>3380700.0</v>
+      </c>
+      <c r="CH5" t="n" s="0">
+        <v>3429700.0</v>
+      </c>
+      <c r="CI5" t="n" s="0">
+        <v>3430200.0</v>
+      </c>
+      <c r="CJ5" t="n" s="0">
+        <v>3579000.0</v>
+      </c>
+      <c r="CK5" t="n" s="0">
+        <v>3521400.0</v>
+      </c>
+      <c r="CL5" t="n" s="0">
+        <v>3305400.0</v>
+      </c>
+      <c r="CM5" t="n" s="0">
+        <v>3367000.0</v>
+      </c>
+      <c r="CN5" t="n" s="0">
+        <v>3387400.0</v>
+      </c>
+      <c r="CO5" t="n" s="0">
+        <v>3346700.0</v>
+      </c>
+      <c r="CP5" t="n" s="0">
+        <v>3361000.0</v>
+      </c>
+      <c r="CQ5" t="n" s="0">
+        <v>3405100.0</v>
+      </c>
+      <c r="CR5" t="n" s="0">
+        <v>3569900.0</v>
+      </c>
+      <c r="CS5" t="n" s="0">
+        <v>3261200.0</v>
+      </c>
+      <c r="CT5" t="n" s="0">
+        <v>3310400.0</v>
+      </c>
+      <c r="CU5" t="n" s="0">
+        <v>3432000.0</v>
+      </c>
+      <c r="CV5" t="n" s="0">
+        <v>3452500.0</v>
+      </c>
+      <c r="CW5" t="n" s="0">
+        <v>3576000.0</v>
+      </c>
+      <c r="CX5" t="n" s="0">
+        <v>3515500.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.63354E7</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>2.42171E7</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>2.11829E7</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>2.40161E7</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>2.40859E7</v>
+      </c>
+      <c r="H6" t="n" s="0">
+        <v>2.49806E7</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>2.44108E7</v>
+      </c>
+      <c r="J6" t="n" s="0">
+        <v>2.49164E7</v>
+      </c>
+      <c r="K6" t="n" s="0">
+        <v>2.47011E7</v>
+      </c>
+      <c r="L6" t="n" s="0">
+        <v>1.62456E7</v>
+      </c>
+      <c r="M6" t="n" s="0">
+        <v>1.62968E7</v>
+      </c>
+      <c r="N6" t="n" s="0">
+        <v>1.64875E7</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>1.6314E7</v>
+      </c>
+      <c r="P6" t="n" s="0">
+        <v>1.64474E7</v>
+      </c>
+      <c r="Q6" t="n" s="0">
+        <v>1.61547E7</v>
+      </c>
+      <c r="R6" t="n" s="0">
+        <v>1.63942E7</v>
+      </c>
+      <c r="S6" t="n" s="0">
+        <v>1.72712E7</v>
+      </c>
+      <c r="T6" t="n" s="0">
+        <v>1.64011E7</v>
+      </c>
+      <c r="U6" t="n" s="0">
+        <v>1.63675E7</v>
+      </c>
+      <c r="V6" t="n" s="0">
+        <v>1.63161E7</v>
+      </c>
+      <c r="W6" t="n" s="0">
+        <v>1.68656E7</v>
+      </c>
+      <c r="X6" t="n" s="0">
+        <v>1.66721E7</v>
+      </c>
+      <c r="Y6" t="n" s="0">
+        <v>1.72416E7</v>
+      </c>
+      <c r="Z6" t="n" s="0">
+        <v>1.64412E7</v>
+      </c>
+      <c r="AA6" t="n" s="0">
+        <v>1.65356E7</v>
+      </c>
+      <c r="AB6" t="n" s="0">
+        <v>1.65605E7</v>
+      </c>
+      <c r="AC6" t="n" s="0">
+        <v>1.64328E7</v>
+      </c>
+      <c r="AD6" t="n" s="0">
+        <v>1.62516E7</v>
+      </c>
+      <c r="AE6" t="n" s="0">
+        <v>1.6319E7</v>
+      </c>
+      <c r="AF6" t="n" s="0">
+        <v>1.62367E7</v>
+      </c>
+      <c r="AG6" t="n" s="0">
+        <v>1.60647E7</v>
+      </c>
+      <c r="AH6" t="n" s="0">
+        <v>1.6628E7</v>
+      </c>
+      <c r="AI6" t="n" s="0">
+        <v>1.63078E7</v>
+      </c>
+      <c r="AJ6" t="n" s="0">
+        <v>1.72073E7</v>
+      </c>
+      <c r="AK6" t="n" s="0">
+        <v>1.72453E7</v>
+      </c>
+      <c r="AL6" t="n" s="0">
+        <v>1.62727E7</v>
+      </c>
+      <c r="AM6" t="n" s="0">
+        <v>1.68775E7</v>
+      </c>
+      <c r="AN6" t="n" s="0">
+        <v>1.66771E7</v>
+      </c>
+      <c r="AO6" t="n" s="0">
+        <v>1.68685E7</v>
+      </c>
+      <c r="AP6" t="n" s="0">
+        <v>1.73989E7</v>
+      </c>
+      <c r="AQ6" t="n" s="0">
+        <v>1.87087E7</v>
+      </c>
+      <c r="AR6" t="n" s="0">
+        <v>1.62728E7</v>
+      </c>
+      <c r="AS6" t="n" s="0">
+        <v>1.62224E7</v>
+      </c>
+      <c r="AT6" t="n" s="0">
+        <v>1.63769E7</v>
+      </c>
+      <c r="AU6" t="n" s="0">
+        <v>1.62633E7</v>
+      </c>
+      <c r="AV6" t="n" s="0">
+        <v>1.62256E7</v>
+      </c>
+      <c r="AW6" t="n" s="0">
+        <v>1.78751E7</v>
+      </c>
+      <c r="AX6" t="n" s="0">
+        <v>1.65527E7</v>
+      </c>
+      <c r="AY6" t="n" s="0">
+        <v>1.62972E7</v>
+      </c>
+      <c r="AZ6" t="n" s="0">
+        <v>1.65029E7</v>
+      </c>
+      <c r="BA6" t="n" s="0">
+        <v>1.6529E7</v>
+      </c>
+      <c r="BB6" t="n" s="0">
+        <v>1.62496E7</v>
+      </c>
+      <c r="BC6" t="n" s="0">
+        <v>1.62969E7</v>
+      </c>
+      <c r="BD6" t="n" s="0">
+        <v>1.63015E7</v>
+      </c>
+      <c r="BE6" t="n" s="0">
+        <v>1.64215E7</v>
+      </c>
+      <c r="BF6" t="n" s="0">
+        <v>1.673E7</v>
+      </c>
+      <c r="BG6" t="n" s="0">
+        <v>1.95495E7</v>
+      </c>
+      <c r="BH6" t="n" s="0">
+        <v>1.62062E7</v>
+      </c>
+      <c r="BI6" t="n" s="0">
+        <v>1.68238E7</v>
+      </c>
+      <c r="BJ6" t="n" s="0">
+        <v>1.63278E7</v>
+      </c>
+      <c r="BK6" t="n" s="0">
+        <v>1.62835E7</v>
+      </c>
+      <c r="BL6" t="n" s="0">
+        <v>1.63372E7</v>
+      </c>
+      <c r="BM6" t="n" s="0">
+        <v>1.66769E7</v>
+      </c>
+      <c r="BN6" t="n" s="0">
+        <v>1.65435E7</v>
+      </c>
+      <c r="BO6" t="n" s="0">
+        <v>1.69031E7</v>
+      </c>
+      <c r="BP6" t="n" s="0">
+        <v>1.73395E7</v>
+      </c>
+      <c r="BQ6" t="n" s="0">
+        <v>1.73735E7</v>
+      </c>
+      <c r="BR6" t="n" s="0">
+        <v>1.74804E7</v>
+      </c>
+      <c r="BS6" t="n" s="0">
+        <v>1.71326E7</v>
+      </c>
+      <c r="BT6" t="n" s="0">
+        <v>1.73502E7</v>
+      </c>
+      <c r="BU6" t="n" s="0">
+        <v>1.74305E7</v>
+      </c>
+      <c r="BV6" t="n" s="0">
+        <v>1.75158E7</v>
+      </c>
+      <c r="BW6" t="n" s="0">
+        <v>1.73444E7</v>
+      </c>
+      <c r="BX6" t="n" s="0">
+        <v>1.63827E7</v>
+      </c>
+      <c r="BY6" t="n" s="0">
+        <v>1.66685E7</v>
+      </c>
+      <c r="BZ6" t="n" s="0">
+        <v>1.70344E7</v>
+      </c>
+      <c r="CA6" t="n" s="0">
+        <v>1.74135E7</v>
+      </c>
+      <c r="CB6" t="n" s="0">
+        <v>1.93442E7</v>
+      </c>
+      <c r="CC6" t="n" s="0">
+        <v>1.94811E7</v>
+      </c>
+      <c r="CD6" t="n" s="0">
+        <v>1.64471E7</v>
+      </c>
+      <c r="CE6" t="n" s="0">
+        <v>1.62654E7</v>
+      </c>
+      <c r="CF6" t="n" s="0">
+        <v>1.68391E7</v>
+      </c>
+      <c r="CG6" t="n" s="0">
+        <v>1.61964E7</v>
+      </c>
+      <c r="CH6" t="n" s="0">
+        <v>1.61922E7</v>
+      </c>
+      <c r="CI6" t="n" s="0">
+        <v>1.67641E7</v>
+      </c>
+      <c r="CJ6" t="n" s="0">
+        <v>1.64127E7</v>
+      </c>
+      <c r="CK6" t="n" s="0">
+        <v>1.67552E7</v>
+      </c>
+      <c r="CL6" t="n" s="0">
+        <v>1.61497E7</v>
+      </c>
+      <c r="CM6" t="n" s="0">
+        <v>1.64589E7</v>
+      </c>
+      <c r="CN6" t="n" s="0">
+        <v>1.64267E7</v>
+      </c>
+      <c r="CO6" t="n" s="0">
+        <v>1.63012E7</v>
+      </c>
+      <c r="CP6" t="n" s="0">
+        <v>1.6227E7</v>
+      </c>
+      <c r="CQ6" t="n" s="0">
+        <v>1.62161E7</v>
+      </c>
+      <c r="CR6" t="n" s="0">
+        <v>1.63356E7</v>
+      </c>
+      <c r="CS6" t="n" s="0">
+        <v>1.6469E7</v>
+      </c>
+      <c r="CT6" t="n" s="0">
+        <v>1.67463E7</v>
+      </c>
+      <c r="CU6" t="n" s="0">
+        <v>1.6132E7</v>
+      </c>
+      <c r="CV6" t="n" s="0">
+        <v>1.62807E7</v>
+      </c>
+      <c r="CW6" t="n" s="0">
+        <v>1.74177E7</v>
+      </c>
+      <c r="CX6" t="n" s="0">
+        <v>1.63491E7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.69697E7</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>2.44375E7</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>1.74209E7</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>2.44627E7</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>2.40702E7</v>
+      </c>
+      <c r="H7" t="n" s="0">
+        <v>2.49856E7</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>2.4536E7</v>
+      </c>
+      <c r="J7" t="n" s="0">
+        <v>2.49299E7</v>
+      </c>
+      <c r="K7" t="n" s="0">
+        <v>2.46566E7</v>
+      </c>
+      <c r="L7" t="n" s="0">
+        <v>1.64289E7</v>
+      </c>
+      <c r="M7" t="n" s="0">
+        <v>1.78275E7</v>
+      </c>
+      <c r="N7" t="n" s="0">
+        <v>1.63617E7</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>1.69525E7</v>
+      </c>
+      <c r="P7" t="n" s="0">
+        <v>1.68753E7</v>
+      </c>
+      <c r="Q7" t="n" s="0">
+        <v>1.61775E7</v>
+      </c>
+      <c r="R7" t="n" s="0">
+        <v>1.66516E7</v>
+      </c>
+      <c r="S7" t="n" s="0">
+        <v>1.63474E7</v>
+      </c>
+      <c r="T7" t="n" s="0">
+        <v>1.62541E7</v>
+      </c>
+      <c r="U7" t="n" s="0">
+        <v>1.62148E7</v>
+      </c>
+      <c r="V7" t="n" s="0">
+        <v>1.64858E7</v>
+      </c>
+      <c r="W7" t="n" s="0">
+        <v>1.64105E7</v>
+      </c>
+      <c r="X7" t="n" s="0">
+        <v>1.62525E7</v>
+      </c>
+      <c r="Y7" t="n" s="0">
+        <v>1.6246E7</v>
+      </c>
+      <c r="Z7" t="n" s="0">
+        <v>1.61472E7</v>
+      </c>
+      <c r="AA7" t="n" s="0">
+        <v>1.66814E7</v>
+      </c>
+      <c r="AB7" t="n" s="0">
+        <v>1.64281E7</v>
+      </c>
+      <c r="AC7" t="n" s="0">
+        <v>1.63863E7</v>
+      </c>
+      <c r="AD7" t="n" s="0">
+        <v>1.66823E7</v>
+      </c>
+      <c r="AE7" t="n" s="0">
+        <v>1.65669E7</v>
+      </c>
+      <c r="AF7" t="n" s="0">
+        <v>1.65293E7</v>
+      </c>
+      <c r="AG7" t="n" s="0">
+        <v>1.63627E7</v>
+      </c>
+      <c r="AH7" t="n" s="0">
+        <v>1.66887E7</v>
+      </c>
+      <c r="AI7" t="n" s="0">
+        <v>1.95031E7</v>
+      </c>
+      <c r="AJ7" t="n" s="0">
+        <v>1.74985E7</v>
+      </c>
+      <c r="AK7" t="n" s="0">
+        <v>1.72752E7</v>
+      </c>
+      <c r="AL7" t="n" s="0">
+        <v>1.70272E7</v>
+      </c>
+      <c r="AM7" t="n" s="0">
+        <v>1.81326E7</v>
+      </c>
+      <c r="AN7" t="n" s="0">
+        <v>1.71969E7</v>
+      </c>
+      <c r="AO7" t="n" s="0">
+        <v>1.70267E7</v>
+      </c>
+      <c r="AP7" t="n" s="0">
+        <v>1.67594E7</v>
+      </c>
+      <c r="AQ7" t="n" s="0">
+        <v>1.927E7</v>
+      </c>
+      <c r="AR7" t="n" s="0">
+        <v>1.65278E7</v>
+      </c>
+      <c r="AS7" t="n" s="0">
+        <v>1.61381E7</v>
+      </c>
+      <c r="AT7" t="n" s="0">
+        <v>1.61632E7</v>
+      </c>
+      <c r="AU7" t="n" s="0">
+        <v>1.63501E7</v>
+      </c>
+      <c r="AV7" t="n" s="0">
+        <v>1.65661E7</v>
+      </c>
+      <c r="AW7" t="n" s="0">
+        <v>1.67569E7</v>
+      </c>
+      <c r="AX7" t="n" s="0">
+        <v>1.64243E7</v>
+      </c>
+      <c r="AY7" t="n" s="0">
+        <v>1.61736E7</v>
+      </c>
+      <c r="AZ7" t="n" s="0">
+        <v>1.61922E7</v>
+      </c>
+      <c r="BA7" t="n" s="0">
+        <v>1.72144E7</v>
+      </c>
+      <c r="BB7" t="n" s="0">
+        <v>1.63965E7</v>
+      </c>
+      <c r="BC7" t="n" s="0">
+        <v>1.76153E7</v>
+      </c>
+      <c r="BD7" t="n" s="0">
+        <v>1.63314E7</v>
+      </c>
+      <c r="BE7" t="n" s="0">
+        <v>1.63943E7</v>
+      </c>
+      <c r="BF7" t="n" s="0">
+        <v>1.62257E7</v>
+      </c>
+      <c r="BG7" t="n" s="0">
+        <v>2.23007E7</v>
+      </c>
+      <c r="BH7" t="n" s="0">
+        <v>1.63382E7</v>
+      </c>
+      <c r="BI7" t="n" s="0">
+        <v>1.81676E7</v>
+      </c>
+      <c r="BJ7" t="n" s="0">
+        <v>1.72374E7</v>
+      </c>
+      <c r="BK7" t="n" s="0">
+        <v>1.65499E7</v>
+      </c>
+      <c r="BL7" t="n" s="0">
+        <v>1.67134E7</v>
+      </c>
+      <c r="BM7" t="n" s="0">
+        <v>1.62611E7</v>
+      </c>
+      <c r="BN7" t="n" s="0">
+        <v>1.73371E7</v>
+      </c>
+      <c r="BO7" t="n" s="0">
+        <v>1.69228E7</v>
+      </c>
+      <c r="BP7" t="n" s="0">
+        <v>1.73572E7</v>
+      </c>
+      <c r="BQ7" t="n" s="0">
+        <v>1.73849E7</v>
+      </c>
+      <c r="BR7" t="n" s="0">
+        <v>1.74501E7</v>
+      </c>
+      <c r="BS7" t="n" s="0">
+        <v>1.65467E7</v>
+      </c>
+      <c r="BT7" t="n" s="0">
+        <v>1.74023E7</v>
+      </c>
+      <c r="BU7" t="n" s="0">
+        <v>1.73959E7</v>
+      </c>
+      <c r="BV7" t="n" s="0">
+        <v>1.7482E7</v>
+      </c>
+      <c r="BW7" t="n" s="0">
+        <v>1.78472E7</v>
+      </c>
+      <c r="BX7" t="n" s="0">
+        <v>1.65871E7</v>
+      </c>
+      <c r="BY7" t="n" s="0">
+        <v>1.67608E7</v>
+      </c>
+      <c r="BZ7" t="n" s="0">
+        <v>1.70833E7</v>
+      </c>
+      <c r="CA7" t="n" s="0">
+        <v>1.72062E7</v>
+      </c>
+      <c r="CB7" t="n" s="0">
+        <v>1.85639E7</v>
+      </c>
+      <c r="CC7" t="n" s="0">
+        <v>1.89211E7</v>
+      </c>
+      <c r="CD7" t="n" s="0">
+        <v>1.66232E7</v>
+      </c>
+      <c r="CE7" t="n" s="0">
+        <v>1.63288E7</v>
+      </c>
+      <c r="CF7" t="n" s="0">
+        <v>1.63877E7</v>
+      </c>
+      <c r="CG7" t="n" s="0">
+        <v>1.66774E7</v>
+      </c>
+      <c r="CH7" t="n" s="0">
+        <v>1.62281E7</v>
+      </c>
+      <c r="CI7" t="n" s="0">
+        <v>1.63732E7</v>
+      </c>
+      <c r="CJ7" t="n" s="0">
+        <v>1.64715E7</v>
+      </c>
+      <c r="CK7" t="n" s="0">
+        <v>1.65519E7</v>
+      </c>
+      <c r="CL7" t="n" s="0">
+        <v>1.67187E7</v>
+      </c>
+      <c r="CM7" t="n" s="0">
+        <v>1.65351E7</v>
+      </c>
+      <c r="CN7" t="n" s="0">
+        <v>1.66666E7</v>
+      </c>
+      <c r="CO7" t="n" s="0">
+        <v>1.62327E7</v>
+      </c>
+      <c r="CP7" t="n" s="0">
+        <v>1.65311E7</v>
+      </c>
+      <c r="CQ7" t="n" s="0">
+        <v>1.61526E7</v>
+      </c>
+      <c r="CR7" t="n" s="0">
+        <v>1.6253E7</v>
+      </c>
+      <c r="CS7" t="n" s="0">
+        <v>1.68397E7</v>
+      </c>
+      <c r="CT7" t="n" s="0">
+        <v>1.61576E7</v>
+      </c>
+      <c r="CU7" t="n" s="0">
+        <v>1.6262E7</v>
+      </c>
+      <c r="CV7" t="n" s="0">
+        <v>1.64722E7</v>
+      </c>
+      <c r="CW7" t="n" s="0">
+        <v>1.76771E7</v>
+      </c>
+      <c r="CX7" t="n" s="0">
+        <v>1.65578E7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>1910500.0</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>984100.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>975900.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>772600.0</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>830100.0</v>
+      </c>
+      <c r="H8" t="n" s="0">
+        <v>1.21338E7</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>1324600.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>1060900.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>958600.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>794900.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>825000.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>801200.0</v>
+      </c>
+      <c r="O8" t="n" s="0">
+        <v>917700.0</v>
+      </c>
+      <c r="P8" t="n" s="0">
+        <v>803400.0</v>
+      </c>
+      <c r="Q8" t="n" s="0">
+        <v>903700.0</v>
+      </c>
+      <c r="R8" t="n" s="0">
+        <v>801300.0</v>
+      </c>
+      <c r="S8" t="n" s="0">
+        <v>983000.0</v>
+      </c>
+      <c r="T8" t="n" s="0">
+        <v>1012700.0</v>
+      </c>
+      <c r="U8" t="n" s="0">
+        <v>920900.0</v>
+      </c>
+      <c r="V8" t="n" s="0">
+        <v>956300.0</v>
+      </c>
+      <c r="W8" t="n" s="0">
+        <v>924500.0</v>
+      </c>
+      <c r="X8" t="n" s="0">
+        <v>911300.0</v>
+      </c>
+      <c r="Y8" t="n" s="0">
+        <v>965100.0</v>
+      </c>
+      <c r="Z8" t="n" s="0">
+        <v>998000.0</v>
+      </c>
+      <c r="AA8" t="n" s="0">
+        <v>934500.0</v>
+      </c>
+      <c r="AB8" t="n" s="0">
+        <v>847000.0</v>
+      </c>
+      <c r="AC8" t="n" s="0">
+        <v>795600.0</v>
+      </c>
+      <c r="AD8" t="n" s="0">
+        <v>852800.0</v>
+      </c>
+      <c r="AE8" t="n" s="0">
+        <v>807600.0</v>
+      </c>
+      <c r="AF8" t="n" s="0">
+        <v>784400.0</v>
+      </c>
+      <c r="AG8" t="n" s="0">
+        <v>801900.0</v>
+      </c>
+      <c r="AH8" t="n" s="0">
+        <v>820000.0</v>
+      </c>
+      <c r="AI8" t="n" s="0">
+        <v>770200.0</v>
+      </c>
+      <c r="AJ8" t="n" s="0">
+        <v>839900.0</v>
+      </c>
+      <c r="AK8" t="n" s="0">
+        <v>881200.0</v>
+      </c>
+      <c r="AL8" t="n" s="0">
+        <v>869600.0</v>
+      </c>
+      <c r="AM8" t="n" s="0">
+        <v>835100.0</v>
+      </c>
+      <c r="AN8" t="n" s="0">
+        <v>802900.0</v>
+      </c>
+      <c r="AO8" t="n" s="0">
+        <v>774200.0</v>
+      </c>
+      <c r="AP8" t="n" s="0">
+        <v>800700.0</v>
+      </c>
+      <c r="AQ8" t="n" s="0">
+        <v>936300.0</v>
+      </c>
+      <c r="AR8" t="n" s="0">
+        <v>1112500.0</v>
+      </c>
+      <c r="AS8" t="n" s="0">
+        <v>994500.0</v>
+      </c>
+      <c r="AT8" t="n" s="0">
+        <v>775300.0</v>
+      </c>
+      <c r="AU8" t="n" s="0">
+        <v>959900.0</v>
+      </c>
+      <c r="AV8" t="n" s="0">
+        <v>936700.0</v>
+      </c>
+      <c r="AW8" t="n" s="0">
+        <v>938000.0</v>
+      </c>
+      <c r="AX8" t="n" s="0">
+        <v>966500.0</v>
+      </c>
+      <c r="AY8" t="n" s="0">
+        <v>763600.0</v>
+      </c>
+      <c r="AZ8" t="n" s="0">
+        <v>754600.0</v>
+      </c>
+      <c r="BA8" t="n" s="0">
+        <v>775100.0</v>
+      </c>
+      <c r="BB8" t="n" s="0">
+        <v>847600.0</v>
+      </c>
+      <c r="BC8" t="n" s="0">
+        <v>4.54046E7</v>
+      </c>
+      <c r="BD8" t="n" s="0">
+        <v>778000.0</v>
+      </c>
+      <c r="BE8" t="n" s="0">
+        <v>888500.0</v>
+      </c>
+      <c r="BF8" t="n" s="0">
+        <v>765700.0</v>
+      </c>
+      <c r="BG8" t="n" s="0">
+        <v>919500.0</v>
+      </c>
+      <c r="BH8" t="n" s="0">
+        <v>967900.0</v>
+      </c>
+      <c r="BI8" t="n" s="0">
+        <v>994500.0</v>
+      </c>
+      <c r="BJ8" t="n" s="0">
+        <v>795200.0</v>
+      </c>
+      <c r="BK8" t="n" s="0">
+        <v>924300.0</v>
+      </c>
+      <c r="BL8" t="n" s="0">
+        <v>962600.0</v>
+      </c>
+      <c r="BM8" t="n" s="0">
+        <v>1089200.0</v>
+      </c>
+      <c r="BN8" t="n" s="0">
+        <v>1016900.0</v>
+      </c>
+      <c r="BO8" t="n" s="0">
+        <v>1024600.0</v>
+      </c>
+      <c r="BP8" t="n" s="0">
+        <v>1011400.0</v>
+      </c>
+      <c r="BQ8" t="n" s="0">
+        <v>810500.0</v>
+      </c>
+      <c r="BR8" t="n" s="0">
+        <v>859100.0</v>
+      </c>
+      <c r="BS8" t="n" s="0">
+        <v>849800.0</v>
+      </c>
+      <c r="BT8" t="n" s="0">
+        <v>840900.0</v>
+      </c>
+      <c r="BU8" t="n" s="0">
+        <v>854300.0</v>
+      </c>
+      <c r="BV8" t="n" s="0">
+        <v>857500.0</v>
+      </c>
+      <c r="BW8" t="n" s="0">
+        <v>5.06462E7</v>
+      </c>
+      <c r="BX8" t="n" s="0">
+        <v>770800.0</v>
+      </c>
+      <c r="BY8" t="n" s="0">
+        <v>774800.0</v>
+      </c>
+      <c r="BZ8" t="n" s="0">
+        <v>837600.0</v>
+      </c>
+      <c r="CA8" t="n" s="0">
+        <v>827600.0</v>
+      </c>
+      <c r="CB8" t="n" s="0">
+        <v>869600.0</v>
+      </c>
+      <c r="CC8" t="n" s="0">
+        <v>1001400.0</v>
+      </c>
+      <c r="CD8" t="n" s="0">
+        <v>994600.0</v>
+      </c>
+      <c r="CE8" t="n" s="0">
+        <v>972300.0</v>
+      </c>
+      <c r="CF8" t="n" s="0">
+        <v>766000.0</v>
+      </c>
+      <c r="CG8" t="n" s="0">
+        <v>830600.0</v>
+      </c>
+      <c r="CH8" t="n" s="0">
+        <v>770400.0</v>
+      </c>
+      <c r="CI8" t="n" s="0">
+        <v>1058100.0</v>
+      </c>
+      <c r="CJ8" t="n" s="0">
+        <v>1079100.0</v>
+      </c>
+      <c r="CK8" t="n" s="0">
+        <v>1135800.0</v>
+      </c>
+      <c r="CL8" t="n" s="0">
+        <v>1697000.0</v>
+      </c>
+      <c r="CM8" t="n" s="0">
+        <v>1042300.0</v>
+      </c>
+      <c r="CN8" t="n" s="0">
+        <v>1108900.0</v>
+      </c>
+      <c r="CO8" t="n" s="0">
+        <v>1090400.0</v>
+      </c>
+      <c r="CP8" t="n" s="0">
+        <v>967700.0</v>
+      </c>
+      <c r="CQ8" t="n" s="0">
+        <v>769300.0</v>
+      </c>
+      <c r="CR8" t="n" s="0">
+        <v>798100.0</v>
+      </c>
+      <c r="CS8" t="n" s="0">
+        <v>778300.0</v>
+      </c>
+      <c r="CT8" t="n" s="0">
+        <v>967600.0</v>
+      </c>
+      <c r="CU8" t="n" s="0">
+        <v>764400.0</v>
+      </c>
+      <c r="CV8" t="n" s="0">
+        <v>814200.0</v>
+      </c>
+      <c r="CW8" t="n" s="0">
+        <v>828000.0</v>
+      </c>
+      <c r="CX8" t="n" s="0">
+        <v>789800.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>3028100.0</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>962700.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>1225400.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>766700.0</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>772700.0</v>
+      </c>
+      <c r="H9" t="n" s="0">
+        <v>878900.0</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>950400.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>954500.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>948200.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>789300.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>805100.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>800000.0</v>
+      </c>
+      <c r="O9" t="n" s="0">
+        <v>895000.0</v>
+      </c>
+      <c r="P9" t="n" s="0">
+        <v>761700.0</v>
+      </c>
+      <c r="Q9" t="n" s="0">
+        <v>934300.0</v>
+      </c>
+      <c r="R9" t="n" s="0">
+        <v>777600.0</v>
+      </c>
+      <c r="S9" t="n" s="0">
+        <v>973300.0</v>
+      </c>
+      <c r="T9" t="n" s="0">
+        <v>904100.0</v>
+      </c>
+      <c r="U9" t="n" s="0">
+        <v>986100.0</v>
+      </c>
+      <c r="V9" t="n" s="0">
+        <v>962600.0</v>
+      </c>
+      <c r="W9" t="n" s="0">
+        <v>1033100.0</v>
+      </c>
+      <c r="X9" t="n" s="0">
+        <v>900100.0</v>
+      </c>
+      <c r="Y9" t="n" s="0">
+        <v>910500.0</v>
+      </c>
+      <c r="Z9" t="n" s="0">
+        <v>909600.0</v>
+      </c>
+      <c r="AA9" t="n" s="0">
+        <v>6.69925E7</v>
+      </c>
+      <c r="AB9" t="n" s="0">
+        <v>809500.0</v>
+      </c>
+      <c r="AC9" t="n" s="0">
+        <v>797500.0</v>
+      </c>
+      <c r="AD9" t="n" s="0">
+        <v>806800.0</v>
+      </c>
+      <c r="AE9" t="n" s="0">
+        <v>808900.0</v>
+      </c>
+      <c r="AF9" t="n" s="0">
+        <v>767000.0</v>
+      </c>
+      <c r="AG9" t="n" s="0">
+        <v>1412700.0</v>
+      </c>
+      <c r="AH9" t="n" s="0">
+        <v>802500.0</v>
+      </c>
+      <c r="AI9" t="n" s="0">
+        <v>809000.0</v>
+      </c>
+      <c r="AJ9" t="n" s="0">
+        <v>897100.0</v>
+      </c>
+      <c r="AK9" t="n" s="0">
+        <v>878700.0</v>
+      </c>
+      <c r="AL9" t="n" s="0">
+        <v>802700.0</v>
+      </c>
+      <c r="AM9" t="n" s="0">
+        <v>973300.0</v>
+      </c>
+      <c r="AN9" t="n" s="0">
+        <v>817300.0</v>
+      </c>
+      <c r="AO9" t="n" s="0">
+        <v>781900.0</v>
+      </c>
+      <c r="AP9" t="n" s="0">
+        <v>815200.0</v>
+      </c>
+      <c r="AQ9" t="n" s="0">
+        <v>876400.0</v>
+      </c>
+      <c r="AR9" t="n" s="0">
+        <v>952000.0</v>
+      </c>
+      <c r="AS9" t="n" s="0">
+        <v>911500.0</v>
+      </c>
+      <c r="AT9" t="n" s="0">
+        <v>767200.0</v>
+      </c>
+      <c r="AU9" t="n" s="0">
+        <v>929900.0</v>
+      </c>
+      <c r="AV9" t="n" s="0">
+        <v>1133100.0</v>
+      </c>
+      <c r="AW9" t="n" s="0">
+        <v>929300.0</v>
+      </c>
+      <c r="AX9" t="n" s="0">
+        <v>935100.0</v>
+      </c>
+      <c r="AY9" t="n" s="0">
+        <v>858800.0</v>
+      </c>
+      <c r="AZ9" t="n" s="0">
+        <v>771900.0</v>
+      </c>
+      <c r="BA9" t="n" s="0">
+        <v>760400.0</v>
+      </c>
+      <c r="BB9" t="n" s="0">
+        <v>787800.0</v>
+      </c>
+      <c r="BC9" t="n" s="0">
+        <v>918200.0</v>
+      </c>
+      <c r="BD9" t="n" s="0">
+        <v>761500.0</v>
+      </c>
+      <c r="BE9" t="n" s="0">
+        <v>795100.0</v>
+      </c>
+      <c r="BF9" t="n" s="0">
+        <v>805300.0</v>
+      </c>
+      <c r="BG9" t="n" s="0">
+        <v>891800.0</v>
+      </c>
+      <c r="BH9" t="n" s="0">
+        <v>927900.0</v>
+      </c>
+      <c r="BI9" t="n" s="0">
+        <v>955800.0</v>
+      </c>
+      <c r="BJ9" t="n" s="0">
+        <v>798100.0</v>
+      </c>
+      <c r="BK9" t="n" s="0">
+        <v>921300.0</v>
+      </c>
+      <c r="BL9" t="n" s="0">
+        <v>956100.0</v>
+      </c>
+      <c r="BM9" t="n" s="0">
+        <v>948600.0</v>
+      </c>
+      <c r="BN9" t="n" s="0">
+        <v>970100.0</v>
+      </c>
+      <c r="BO9" t="n" s="0">
+        <v>997500.0</v>
+      </c>
+      <c r="BP9" t="n" s="0">
+        <v>995100.0</v>
+      </c>
+      <c r="BQ9" t="n" s="0">
+        <v>820000.0</v>
+      </c>
+      <c r="BR9" t="n" s="0">
+        <v>817400.0</v>
+      </c>
+      <c r="BS9" t="n" s="0">
+        <v>801500.0</v>
+      </c>
+      <c r="BT9" t="n" s="0">
+        <v>810300.0</v>
+      </c>
+      <c r="BU9" t="n" s="0">
+        <v>866200.0</v>
+      </c>
+      <c r="BV9" t="n" s="0">
+        <v>859600.0</v>
+      </c>
+      <c r="BW9" t="n" s="0">
+        <v>908900.0</v>
+      </c>
+      <c r="BX9" t="n" s="0">
+        <v>766000.0</v>
+      </c>
+      <c r="BY9" t="n" s="0">
+        <v>760700.0</v>
+      </c>
+      <c r="BZ9" t="n" s="0">
+        <v>954600.0</v>
+      </c>
+      <c r="CA9" t="n" s="0">
+        <v>814400.0</v>
+      </c>
+      <c r="CB9" t="n" s="0">
+        <v>1027600.0</v>
+      </c>
+      <c r="CC9" t="n" s="0">
+        <v>1062600.0</v>
+      </c>
+      <c r="CD9" t="n" s="0">
+        <v>934100.0</v>
+      </c>
+      <c r="CE9" t="n" s="0">
+        <v>929200.0</v>
+      </c>
+      <c r="CF9" t="n" s="0">
+        <v>786900.0</v>
+      </c>
+      <c r="CG9" t="n" s="0">
+        <v>784000.0</v>
+      </c>
+      <c r="CH9" t="n" s="0">
+        <v>779900.0</v>
+      </c>
+      <c r="CI9" t="n" s="0">
+        <v>1023000.0</v>
+      </c>
+      <c r="CJ9" t="n" s="0">
+        <v>1115700.0</v>
+      </c>
+      <c r="CK9" t="n" s="0">
+        <v>1107900.0</v>
+      </c>
+      <c r="CL9" t="n" s="0">
+        <v>1088800.0</v>
+      </c>
+      <c r="CM9" t="n" s="0">
+        <v>1096700.0</v>
+      </c>
+      <c r="CN9" t="n" s="0">
+        <v>1036900.0</v>
+      </c>
+      <c r="CO9" t="n" s="0">
+        <v>1192100.0</v>
+      </c>
+      <c r="CP9" t="n" s="0">
+        <v>766500.0</v>
+      </c>
+      <c r="CQ9" t="n" s="0">
+        <v>774600.0</v>
+      </c>
+      <c r="CR9" t="n" s="0">
+        <v>783000.0</v>
+      </c>
+      <c r="CS9" t="n" s="0">
+        <v>785900.0</v>
+      </c>
+      <c r="CT9" t="n" s="0">
+        <v>814900.0</v>
+      </c>
+      <c r="CU9" t="n" s="0">
+        <v>770400.0</v>
+      </c>
+      <c r="CV9" t="n" s="0">
+        <v>775700.0</v>
+      </c>
+      <c r="CW9" t="n" s="0">
+        <v>837500.0</v>
+      </c>
+      <c r="CX9" t="n" s="0">
+        <v>786700.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>1.23967E7</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>1307000.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>1370000.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>968000.0</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>972100.0</v>
+      </c>
+      <c r="H10" t="n" s="0">
+        <v>1011600.0</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>1161900.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>1196800.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>1191000.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>929800.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>888300.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>1033000.0</v>
+      </c>
+      <c r="O10" t="n" s="0">
+        <v>1033000.0</v>
+      </c>
+      <c r="P10" t="n" s="0">
+        <v>1005200.0</v>
+      </c>
+      <c r="Q10" t="n" s="0">
+        <v>1577400.0</v>
+      </c>
+      <c r="R10" t="n" s="0">
+        <v>947600.0</v>
+      </c>
+      <c r="S10" t="n" s="0">
+        <v>1203000.0</v>
+      </c>
+      <c r="T10" t="n" s="0">
+        <v>1173400.0</v>
+      </c>
+      <c r="U10" t="n" s="0">
+        <v>1246500.0</v>
+      </c>
+      <c r="V10" t="n" s="0">
+        <v>1276300.0</v>
+      </c>
+      <c r="W10" t="n" s="0">
+        <v>1263700.0</v>
+      </c>
+      <c r="X10" t="n" s="0">
+        <v>1577500.0</v>
+      </c>
+      <c r="Y10" t="n" s="0">
+        <v>1206700.0</v>
+      </c>
+      <c r="Z10" t="n" s="0">
+        <v>1138200.0</v>
+      </c>
+      <c r="AA10" t="n" s="0">
+        <v>1020800.0</v>
+      </c>
+      <c r="AB10" t="n" s="0">
+        <v>962600.0</v>
+      </c>
+      <c r="AC10" t="n" s="0">
+        <v>898000.0</v>
+      </c>
+      <c r="AD10" t="n" s="0">
+        <v>912000.0</v>
+      </c>
+      <c r="AE10" t="n" s="0">
+        <v>959000.0</v>
+      </c>
+      <c r="AF10" t="n" s="0">
+        <v>934500.0</v>
+      </c>
+      <c r="AG10" t="n" s="0">
+        <v>1067400.0</v>
+      </c>
+      <c r="AH10" t="n" s="0">
+        <v>983200.0</v>
+      </c>
+      <c r="AI10" t="n" s="0">
+        <v>963200.0</v>
+      </c>
+      <c r="AJ10" t="n" s="0">
+        <v>929000.0</v>
+      </c>
+      <c r="AK10" t="n" s="0">
+        <v>1065700.0</v>
+      </c>
+      <c r="AL10" t="n" s="0">
+        <v>1089500.0</v>
+      </c>
+      <c r="AM10" t="n" s="0">
+        <v>1003800.0</v>
+      </c>
+      <c r="AN10" t="n" s="0">
+        <v>1037800.0</v>
+      </c>
+      <c r="AO10" t="n" s="0">
+        <v>1019300.0</v>
+      </c>
+      <c r="AP10" t="n" s="0">
+        <v>1071200.0</v>
+      </c>
+      <c r="AQ10" t="n" s="0">
+        <v>1096100.0</v>
+      </c>
+      <c r="AR10" t="n" s="0">
+        <v>1205700.0</v>
+      </c>
+      <c r="AS10" t="n" s="0">
+        <v>4.313E7</v>
+      </c>
+      <c r="AT10" t="n" s="0">
+        <v>1005100.0</v>
+      </c>
+      <c r="AU10" t="n" s="0">
+        <v>1211400.0</v>
+      </c>
+      <c r="AV10" t="n" s="0">
+        <v>1190600.0</v>
+      </c>
+      <c r="AW10" t="n" s="0">
+        <v>1160400.0</v>
+      </c>
+      <c r="AX10" t="n" s="0">
+        <v>1247100.0</v>
+      </c>
+      <c r="AY10" t="n" s="0">
+        <v>933200.0</v>
+      </c>
+      <c r="AZ10" t="n" s="0">
+        <v>967500.0</v>
+      </c>
+      <c r="BA10" t="n" s="0">
+        <v>992600.0</v>
+      </c>
+      <c r="BB10" t="n" s="0">
+        <v>928800.0</v>
+      </c>
+      <c r="BC10" t="n" s="0">
+        <v>992500.0</v>
+      </c>
+      <c r="BD10" t="n" s="0">
+        <v>1093300.0</v>
+      </c>
+      <c r="BE10" t="n" s="0">
+        <v>1063200.0</v>
+      </c>
+      <c r="BF10" t="n" s="0">
+        <v>918100.0</v>
+      </c>
+      <c r="BG10" t="n" s="0">
+        <v>1066100.0</v>
+      </c>
+      <c r="BH10" t="n" s="0">
+        <v>1202100.0</v>
+      </c>
+      <c r="BI10" t="n" s="0">
+        <v>1242100.0</v>
+      </c>
+      <c r="BJ10" t="n" s="0">
+        <v>892300.0</v>
+      </c>
+      <c r="BK10" t="n" s="0">
+        <v>1159000.0</v>
+      </c>
+      <c r="BL10" t="n" s="0">
+        <v>1306100.0</v>
+      </c>
+      <c r="BM10" t="n" s="0">
+        <v>1137200.0</v>
+      </c>
+      <c r="BN10" t="n" s="0">
+        <v>1258400.0</v>
+      </c>
+      <c r="BO10" t="n" s="0">
+        <v>1341500.0</v>
+      </c>
+      <c r="BP10" t="n" s="0">
+        <v>1339900.0</v>
+      </c>
+      <c r="BQ10" t="n" s="0">
+        <v>1070900.0</v>
+      </c>
+      <c r="BR10" t="n" s="0">
+        <v>1032300.0</v>
+      </c>
+      <c r="BS10" t="n" s="0">
+        <v>1016900.0</v>
+      </c>
+      <c r="BT10" t="n" s="0">
+        <v>1037100.0</v>
+      </c>
+      <c r="BU10" t="n" s="0">
+        <v>949800.0</v>
+      </c>
+      <c r="BV10" t="n" s="0">
+        <v>1087300.0</v>
+      </c>
+      <c r="BW10" t="n" s="0">
+        <v>1024800.0</v>
+      </c>
+      <c r="BX10" t="n" s="0">
+        <v>1013000.0</v>
+      </c>
+      <c r="BY10" t="n" s="0">
+        <v>941600.0</v>
+      </c>
+      <c r="BZ10" t="n" s="0">
+        <v>949600.0</v>
+      </c>
+      <c r="CA10" t="n" s="0">
+        <v>1052900.0</v>
+      </c>
+      <c r="CB10" t="n" s="0">
+        <v>1079100.0</v>
+      </c>
+      <c r="CC10" t="n" s="0">
+        <v>1330300.0</v>
+      </c>
+      <c r="CD10" t="n" s="0">
+        <v>1190500.0</v>
+      </c>
+      <c r="CE10" t="n" s="0">
+        <v>1189900.0</v>
+      </c>
+      <c r="CF10" t="n" s="0">
+        <v>1008800.0</v>
+      </c>
+      <c r="CG10" t="n" s="0">
+        <v>1065400.0</v>
+      </c>
+      <c r="CH10" t="n" s="0">
+        <v>1002300.0</v>
+      </c>
+      <c r="CI10" t="n" s="0">
+        <v>1302000.0</v>
+      </c>
+      <c r="CJ10" t="n" s="0">
+        <v>1351800.0</v>
+      </c>
+      <c r="CK10" t="n" s="0">
+        <v>1444800.0</v>
+      </c>
+      <c r="CL10" t="n" s="0">
+        <v>1456600.0</v>
+      </c>
+      <c r="CM10" t="n" s="0">
+        <v>1439400.0</v>
+      </c>
+      <c r="CN10" t="n" s="0">
+        <v>1469500.0</v>
+      </c>
+      <c r="CO10" t="n" s="0">
+        <v>1458400.0</v>
+      </c>
+      <c r="CP10" t="n" s="0">
+        <v>1053500.0</v>
+      </c>
+      <c r="CQ10" t="n" s="0">
+        <v>998600.0</v>
+      </c>
+      <c r="CR10" t="n" s="0">
+        <v>924000.0</v>
+      </c>
+      <c r="CS10" t="n" s="0">
+        <v>951800.0</v>
+      </c>
+      <c r="CT10" t="n" s="0">
+        <v>938800.0</v>
+      </c>
+      <c r="CU10" t="n" s="0">
+        <v>956800.0</v>
+      </c>
+      <c r="CV10" t="n" s="0">
+        <v>996900.0</v>
+      </c>
+      <c r="CW10" t="n" s="0">
+        <v>951100.0</v>
+      </c>
+      <c r="CX10" t="n" s="0">
+        <v>956700.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>3433400.0</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>1197500.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>1276000.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>992300.0</v>
+      </c>
+      <c r="G11" t="n" s="0">
+        <v>982000.0</v>
+      </c>
+      <c r="H11" t="n" s="0">
+        <v>1066300.0</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>1186400.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>1320300.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>1204400.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>1017300.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>888500.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>940300.0</v>
+      </c>
+      <c r="O11" t="n" s="0">
+        <v>1002400.0</v>
+      </c>
+      <c r="P11" t="n" s="0">
+        <v>1210600.0</v>
+      </c>
+      <c r="Q11" t="n" s="0">
+        <v>1251900.0</v>
+      </c>
+      <c r="R11" t="n" s="0">
+        <v>904100.0</v>
+      </c>
+      <c r="S11" t="n" s="0">
+        <v>1210400.0</v>
+      </c>
+      <c r="T11" t="n" s="0">
+        <v>1206700.0</v>
+      </c>
+      <c r="U11" t="n" s="0">
+        <v>1342000.0</v>
+      </c>
+      <c r="V11" t="n" s="0">
+        <v>1236300.0</v>
+      </c>
+      <c r="W11" t="n" s="0">
+        <v>1244900.0</v>
+      </c>
+      <c r="X11" t="n" s="0">
+        <v>1144100.0</v>
+      </c>
+      <c r="Y11" t="n" s="0">
+        <v>1244300.0</v>
+      </c>
+      <c r="Z11" t="n" s="0">
+        <v>1158100.0</v>
+      </c>
+      <c r="AA11" t="n" s="0">
+        <v>951600.0</v>
+      </c>
+      <c r="AB11" t="n" s="0">
+        <v>1035000.0</v>
+      </c>
+      <c r="AC11" t="n" s="0">
+        <v>944000.0</v>
+      </c>
+      <c r="AD11" t="n" s="0">
+        <v>1220500.0</v>
+      </c>
+      <c r="AE11" t="n" s="0">
+        <v>1184400.0</v>
+      </c>
+      <c r="AF11" t="n" s="0">
+        <v>1130500.0</v>
+      </c>
+      <c r="AG11" t="n" s="0">
+        <v>992100.0</v>
+      </c>
+      <c r="AH11" t="n" s="0">
+        <v>1103600.0</v>
+      </c>
+      <c r="AI11" t="n" s="0">
+        <v>1168200.0</v>
+      </c>
+      <c r="AJ11" t="n" s="0">
+        <v>1118000.0</v>
+      </c>
+      <c r="AK11" t="n" s="0">
+        <v>954900.0</v>
+      </c>
+      <c r="AL11" t="n" s="0">
+        <v>949300.0</v>
+      </c>
+      <c r="AM11" t="n" s="0">
+        <v>945300.0</v>
+      </c>
+      <c r="AN11" t="n" s="0">
+        <v>1071600.0</v>
+      </c>
+      <c r="AO11" t="n" s="0">
+        <v>1071600.0</v>
+      </c>
+      <c r="AP11" t="n" s="0">
+        <v>1117500.0</v>
+      </c>
+      <c r="AQ11" t="n" s="0">
+        <v>1068900.0</v>
+      </c>
+      <c r="AR11" t="n" s="0">
+        <v>1231400.0</v>
+      </c>
+      <c r="AS11" t="n" s="0">
+        <v>912900.0</v>
+      </c>
+      <c r="AT11" t="n" s="0">
+        <v>1152000.0</v>
+      </c>
+      <c r="AU11" t="n" s="0">
+        <v>1310600.0</v>
+      </c>
+      <c r="AV11" t="n" s="0">
+        <v>1202400.0</v>
+      </c>
+      <c r="AW11" t="n" s="0">
+        <v>1182500.0</v>
+      </c>
+      <c r="AX11" t="n" s="0">
+        <v>1227400.0</v>
+      </c>
+      <c r="AY11" t="n" s="0">
+        <v>990800.0</v>
+      </c>
+      <c r="AZ11" t="n" s="0">
+        <v>985300.0</v>
+      </c>
+      <c r="BA11" t="n" s="0">
+        <v>886000.0</v>
+      </c>
+      <c r="BB11" t="n" s="0">
+        <v>1007500.0</v>
+      </c>
+      <c r="BC11" t="n" s="0">
+        <v>1088100.0</v>
+      </c>
+      <c r="BD11" t="n" s="0">
+        <v>1073000.0</v>
+      </c>
+      <c r="BE11" t="n" s="0">
+        <v>991300.0</v>
+      </c>
+      <c r="BF11" t="n" s="0">
+        <v>1004000.0</v>
+      </c>
+      <c r="BG11" t="n" s="0">
+        <v>1130900.0</v>
+      </c>
+      <c r="BH11" t="n" s="0">
+        <v>1178900.0</v>
+      </c>
+      <c r="BI11" t="n" s="0">
+        <v>1455400.0</v>
+      </c>
+      <c r="BJ11" t="n" s="0">
+        <v>1068200.0</v>
+      </c>
+      <c r="BK11" t="n" s="0">
+        <v>1268800.0</v>
+      </c>
+      <c r="BL11" t="n" s="0">
+        <v>1194400.0</v>
+      </c>
+      <c r="BM11" t="n" s="0">
+        <v>1217500.0</v>
+      </c>
+      <c r="BN11" t="n" s="0">
+        <v>1215400.0</v>
+      </c>
+      <c r="BO11" t="n" s="0">
+        <v>1282200.0</v>
+      </c>
+      <c r="BP11" t="n" s="0">
+        <v>1278000.0</v>
+      </c>
+      <c r="BQ11" t="n" s="0">
+        <v>974600.0</v>
+      </c>
+      <c r="BR11" t="n" s="0">
+        <v>1107900.0</v>
+      </c>
+      <c r="BS11" t="n" s="0">
+        <v>1002200.0</v>
+      </c>
+      <c r="BT11" t="n" s="0">
+        <v>977700.0</v>
+      </c>
+      <c r="BU11" t="n" s="0">
+        <v>1155100.0</v>
+      </c>
+      <c r="BV11" t="n" s="0">
+        <v>1006700.0</v>
+      </c>
+      <c r="BW11" t="n" s="0">
+        <v>1132400.0</v>
+      </c>
+      <c r="BX11" t="n" s="0">
+        <v>1111400.0</v>
+      </c>
+      <c r="BY11" t="n" s="0">
+        <v>1094800.0</v>
+      </c>
+      <c r="BZ11" t="n" s="0">
+        <v>942000.0</v>
+      </c>
+      <c r="CA11" t="n" s="0">
+        <v>1204500.0</v>
+      </c>
+      <c r="CB11" t="n" s="0">
+        <v>1028500.0</v>
+      </c>
+      <c r="CC11" t="n" s="0">
+        <v>1321900.0</v>
+      </c>
+      <c r="CD11" t="n" s="0">
+        <v>1113500.0</v>
+      </c>
+      <c r="CE11" t="n" s="0">
+        <v>1177000.0</v>
+      </c>
+      <c r="CF11" t="n" s="0">
+        <v>1168500.0</v>
+      </c>
+      <c r="CG11" t="n" s="0">
+        <v>959400.0</v>
+      </c>
+      <c r="CH11" t="n" s="0">
+        <v>1226700.0</v>
+      </c>
+      <c r="CI11" t="n" s="0">
+        <v>1286500.0</v>
+      </c>
+      <c r="CJ11" t="n" s="0">
+        <v>1866900.0</v>
+      </c>
+      <c r="CK11" t="n" s="0">
+        <v>1925300.0</v>
+      </c>
+      <c r="CL11" t="n" s="0">
+        <v>3130900.0</v>
+      </c>
+      <c r="CM11" t="n" s="0">
+        <v>1896900.0</v>
+      </c>
+      <c r="CN11" t="n" s="0">
+        <v>1341100.0</v>
+      </c>
+      <c r="CO11" t="n" s="0">
+        <v>1533800.0</v>
+      </c>
+      <c r="CP11" t="n" s="0">
+        <v>1186900.0</v>
+      </c>
+      <c r="CQ11" t="n" s="0">
+        <v>1385100.0</v>
+      </c>
+      <c r="CR11" t="n" s="0">
+        <v>906500.0</v>
+      </c>
+      <c r="CS11" t="n" s="0">
+        <v>912400.0</v>
+      </c>
+      <c r="CT11" t="n" s="0">
+        <v>982100.0</v>
+      </c>
+      <c r="CU11" t="n" s="0">
+        <v>1196800.0</v>
+      </c>
+      <c r="CV11" t="n" s="0">
+        <v>1054700.0</v>
+      </c>
+      <c r="CW11" t="n" s="0">
+        <v>955700.0</v>
+      </c>
+      <c r="CX11" t="n" s="0">
+        <v>976000.0</v>
       </c>
     </row>
   </sheetData>
